--- a/tools/importer/reports/import-chess-challenge.report.xlsx
+++ b/tools/importer/reports/import-chess-challenge.report.xlsx
@@ -127,7 +127,7 @@
     <t>fr/fr/chess-challenge.report.json</t>
   </si>
   <si>
-    <t>["age-gate","player-registration","chess","invite"]</t>
+    <t>["age-gate","player-registration","chess","invite","player-message"]</t>
   </si>
   <si>
     <t>fr/fr/chess-challenge</t>
@@ -136,7 +136,7 @@
     <t>chess-challenge</t>
   </si>
   <si>
-    <t>2026-10-16T13:36:39.459Z</t>
+    <t>2026-10-21T09:30:31.524Z</t>
   </si>
   <si>
     <t>Le Suze Chess Challenge</t>
@@ -154,7 +154,7 @@
     <t>masters/en/chess-challenge</t>
   </si>
   <si>
-    <t>2026-10-16T13:36:29.433Z</t>
+    <t>2026-10-21T09:30:21.631Z</t>
   </si>
   <si>
     <t>The Suze Chess Challenge</t>
@@ -169,7 +169,7 @@
     <t>us/es/chess-challenge</t>
   </si>
   <si>
-    <t>2026-10-16T13:36:33.656Z</t>
+    <t>2026-10-21T09:30:25.922Z</t>
   </si>
   <si>
     <t>El Suze Chess Challenge</t>
@@ -184,7 +184,7 @@
     <t>experiments/fr/fr/chess-challenge/exp-chess-001/challenger</t>
   </si>
   <si>
-    <t>2026-10-16T13:36:53.830Z</t>
+    <t>2026-10-21T09:30:44.469Z</t>
   </si>
   <si>
     <t>http://localhost:3000/tools/importer/sources/chess-challenge/fr-fr.html?variant=challenger</t>
@@ -199,7 +199,7 @@
     <t>experiments/masters/en/chess-challenge/exp-chess-001/challenger</t>
   </si>
   <si>
-    <t>2026-10-16T13:36:44.487Z</t>
+    <t>2026-10-21T09:30:35.169Z</t>
   </si>
   <si>
     <t>http://localhost:3000/tools/importer/sources/chess-challenge/masters-en.html?variant=challenger</t>
@@ -211,7 +211,7 @@
     <t>experiments/us/es/chess-challenge/exp-chess-001/challenger</t>
   </si>
   <si>
-    <t>2026-10-16T13:36:48.610Z</t>
+    <t>2026-10-21T09:30:40.224Z</t>
   </si>
   <si>
     <t>http://localhost:3000/tools/importer/sources/chess-challenge/us-es.html?variant=challenger</t>

--- a/tools/importer/reports/import-chess-challenge.report.xlsx
+++ b/tools/importer/reports/import-chess-challenge.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="72">
   <si>
     <t>_reportFile</t>
   </si>
@@ -136,7 +136,7 @@
     <t>chess-challenge</t>
   </si>
   <si>
-    <t>2026-10-21T09:30:31.524Z</t>
+    <t>2026-10-26T09:32:36.990Z</t>
   </si>
   <si>
     <t>Le Suze Chess Challenge</t>
@@ -154,7 +154,7 @@
     <t>masters/en/chess-challenge</t>
   </si>
   <si>
-    <t>2026-10-21T09:30:21.631Z</t>
+    <t>2026-10-26T09:32:28.854Z</t>
   </si>
   <si>
     <t>The Suze Chess Challenge</t>
@@ -169,7 +169,7 @@
     <t>us/es/chess-challenge</t>
   </si>
   <si>
-    <t>2026-10-21T09:30:25.922Z</t>
+    <t>2026-10-26T09:32:32.985Z</t>
   </si>
   <si>
     <t>El Suze Chess Challenge</t>
@@ -184,7 +184,7 @@
     <t>experiments/fr/fr/chess-challenge/exp-chess-001/challenger</t>
   </si>
   <si>
-    <t>2026-10-21T09:30:44.469Z</t>
+    <t>2026-10-26T09:32:48.300Z</t>
   </si>
   <si>
     <t>http://localhost:3000/tools/importer/sources/chess-challenge/fr-fr.html?variant=challenger</t>
@@ -205,13 +205,25 @@
     <t>http://localhost:3000/tools/importer/sources/chess-challenge/masters-en.html?variant=challenger</t>
   </si>
   <si>
+    <t>experiments/us/en/chess-challenge/exp-chess-001/challenger.report.json</t>
+  </si>
+  <si>
+    <t>experiments/us/en/chess-challenge/exp-chess-001/challenger</t>
+  </si>
+  <si>
+    <t>2026-10-26T09:32:52.621Z</t>
+  </si>
+  <si>
+    <t>http://localhost:3000/tools/importer/sources/chess-challenge/us-en.html?variant=challenger</t>
+  </si>
+  <si>
     <t>experiments/us/es/chess-challenge/exp-chess-001/challenger.report.json</t>
   </si>
   <si>
     <t>experiments/us/es/chess-challenge/exp-chess-001/challenger</t>
   </si>
   <si>
-    <t>2026-10-21T09:30:40.224Z</t>
+    <t>2026-10-26T09:32:42.479Z</t>
   </si>
   <si>
     <t>http://localhost:3000/tools/importer/sources/chess-challenge/us-es.html?variant=challenger</t>
@@ -603,7 +615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -923,12 +935,41 @@
         <v>66</v>
       </c>
       <c r="G11" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H11" t="s">
         <v>67</v>
       </c>
       <c r="I11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" t="s">
+        <v>71</v>
+      </c>
+      <c r="I12" t="s">
         <v>59</v>
       </c>
     </row>
